--- a/data/demo/pastdue_home_20260822.xlsx
+++ b/data/demo/pastdue_home_20260822.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2612" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2612" uniqueCount="289">
   <si>
     <t/>
   </si>
@@ -43,7 +43,7 @@
     <t>Expires</t>
   </si>
   <si>
-    <t>Valid Vehicle Insurance Expires (Rivian)</t>
+    <t>Valid Vehicle Insurance Expires (Wendell)</t>
   </si>
   <si>
     <t>Beckett Rasmussen-Tanaka</t>
@@ -79,16 +79,16 @@
     <t>Ondrejka-Iverson, Lorcan</t>
   </si>
   <si>
-    <t>Valid Vehicle Insurance Expires (Prius Prime)</t>
+    <t>Valid Vehicle Insurance Expires (Osric)</t>
   </si>
   <si>
     <t>Hollis-Farrow, Lorcan D.</t>
   </si>
   <si>
-    <t>Valid Vehicle Insurance Expires (Highlander)</t>
-  </si>
-  <si>
-    <t>Valid Vehicle Insurance Expires (Range Rover)</t>
+    <t>Valid Vehicle Insurance Expires (Sable)</t>
+  </si>
+  <si>
+    <t>Valid Vehicle Insurance Expires (Yarrow)</t>
   </si>
   <si>
     <t>Odalys Gallagher-Prescott</t>
@@ -109,7 +109,7 @@
     <t>Jarrett-Vasquez, Keziah</t>
   </si>
   <si>
-    <t>Valid Vehicle Insurance Expires (Nissan)</t>
+    <t>Valid Vehicle Insurance Expires (Cassian)</t>
   </si>
   <si>
     <t>Quimby-Zabala, Zora</t>
@@ -133,13 +133,13 @@
     <t>Hargrove-Gallagher, Gemma</t>
   </si>
   <si>
-    <t>Valid Vehicle Insurance Expires (Mercedes)</t>
+    <t>Valid Vehicle Insurance Expires (Zinnia)</t>
   </si>
   <si>
     <t>Gallagher-Iverson, Vidal</t>
   </si>
   <si>
-    <t>Houston Strong Town Hall Meeting #1 Expires (Shalaundra)</t>
+    <t>Houston Strong Town Hall Meeting #1 Expires (Anouk)</t>
   </si>
   <si>
     <t>Xavier Fontaine-Waverly</t>
@@ -148,7 +148,7 @@
     <t>Dunmore-Fontaine, Uma</t>
   </si>
   <si>
-    <t>EBI Expires (Tequilla, Shadonna)</t>
+    <t>EBI Expires (Halcyon, Linnea)</t>
   </si>
   <si>
     <t>Kowalski-Ashford, Beckett J.</t>
@@ -166,7 +166,7 @@
     <t>Quincy Silvestri-Jarrett</t>
   </si>
   <si>
-    <t>Valid Vehicle Insurance Expires (Toyota)</t>
+    <t>Valid Vehicle Insurance Expires (Jethro)</t>
   </si>
   <si>
     <t>Thaddeus Silvestri-Ueda</t>
@@ -178,13 +178,13 @@
     <t>Emergency Severe Weather and Fire Drill Log Expires</t>
   </si>
   <si>
-    <t>Valid Drivers License Expires (Mary)</t>
+    <t>Valid Drivers License Expires (Rowan)</t>
   </si>
   <si>
     <t>Pemberton-Quintero, Nadia L.</t>
   </si>
   <si>
-    <t>Shaken Baby Syndrome Expires (Twyla)</t>
+    <t>Shaken Baby Syndrome Expires (Rowan)</t>
   </si>
   <si>
     <t>Dmitri Larkin-Thibodeaux</t>
@@ -205,7 +205,7 @@
     <t>Carver-Ueda, Rafferty</t>
   </si>
   <si>
-    <t>First Aid and CPR Expires (Twyla)</t>
+    <t>First Aid and CPR Expires (Rowan)</t>
   </si>
   <si>
     <t>Ulises Farrow-Ueda</t>
@@ -217,13 +217,13 @@
     <t>Quincy Jennings-Gallagher</t>
   </si>
   <si>
-    <t>Normalcy Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Reporting Child Abuse and Neglect Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (2hrs) Expires (Twyla)</t>
+    <t>Normalcy Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Reporting Child Abuse and Neglect Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Trauma Informed Care (2hrs) Expires (Rowan)</t>
   </si>
   <si>
     <t>Adaeze Ondrejka-Quintero</t>
@@ -232,10 +232,10 @@
     <t>Silvestri-Underhill, Willa</t>
   </si>
   <si>
-    <t>Reporting Child Abuse and Neglect Expires (Joseph)</t>
-  </si>
-  <si>
-    <t>Separation and Loss Expires (Twyla)</t>
+    <t>Reporting Child Abuse and Neglect Expires (Perpetua)</t>
+  </si>
+  <si>
+    <t>Separation and Loss Expires (Rowan)</t>
   </si>
   <si>
     <t>Sandoval-Underhill, Maeve A.</t>
@@ -244,7 +244,7 @@
     <t>Tamsin Zabala-Castellanos</t>
   </si>
   <si>
-    <t>Emergency-Disaster Preparedness Expires (Twyla)</t>
+    <t>Emergency-Disaster Preparedness Expires (Rowan)</t>
   </si>
   <si>
     <t>Fire Prevention Checklist - Inspection Expires</t>
@@ -253,28 +253,28 @@
     <t>Environmental Health Inspection Expires</t>
   </si>
   <si>
-    <t>Picture of Vehicle Inspection Sticker Expires (Mercedes Benz)</t>
-  </si>
-  <si>
-    <t>Valid Vehicle Insurance Expires (Chrysler)</t>
-  </si>
-  <si>
-    <t>Valid Vehicle Insurance Expires (Mercedes Benz)</t>
-  </si>
-  <si>
-    <t>Bloodborne Pathogens Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Water Safety Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Picture of Vehicle Inspection Sticker Expires (Toyota)</t>
-  </si>
-  <si>
-    <t>Picture of Vehicle Inspection Sticker Expires (Honda)</t>
-  </si>
-  <si>
-    <t>Picture of Vehicle Inspection Sticker Expires (Chrysler)</t>
+    <t>Picture of Vehicle Inspection Sticker Expires (Kestrel)</t>
+  </si>
+  <si>
+    <t>Valid Vehicle Insurance Expires (Quill)</t>
+  </si>
+  <si>
+    <t>Valid Vehicle Insurance Expires (Kestrel)</t>
+  </si>
+  <si>
+    <t>Bloodborne Pathogens Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Water Safety Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Picture of Vehicle Inspection Sticker Expires (Jethro)</t>
+  </si>
+  <si>
+    <t>Picture of Vehicle Inspection Sticker Expires (Ursula)</t>
+  </si>
+  <si>
+    <t>Picture of Vehicle Inspection Sticker Expires (Quill)</t>
   </si>
   <si>
     <t>Zabala-Quimby, Kaia</t>
@@ -301,7 +301,7 @@
     <t>Valid Vehicle Insurance Expires (2023 Kia)</t>
   </si>
   <si>
-    <t>Valid Vehicle Insurance Expires (Honda)</t>
+    <t>Valid Vehicle Insurance Expires (Ursula)</t>
   </si>
   <si>
     <t>Home Insurance Expires</t>
@@ -310,25 +310,25 @@
     <t>Drivers License (Parent B) Expires</t>
   </si>
   <si>
-    <t>Health and Safety Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Cultural Competency Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Sexual Abuse Expires (Tequilla)</t>
-  </si>
-  <si>
-    <t>Sexual Abuse Expires (Shadonna)</t>
-  </si>
-  <si>
-    <t>Minimum Standards Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Medication Management Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Houston Strong Town Hall Meeting #1 Expires (Twyla)</t>
+    <t>Health and Safety Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Cultural Competency Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Sexual Abuse Expires (Halcyon)</t>
+  </si>
+  <si>
+    <t>Sexual Abuse Expires (Linnea)</t>
+  </si>
+  <si>
+    <t>Minimum Standards Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Medication Management Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Houston Strong Town Hall Meeting #1 Expires (Rowan)</t>
   </si>
   <si>
     <t>Hollis-Dunmore, Priya</t>
@@ -352,10 +352,10 @@
     <t>Jarrett-Yoshida, Finnian G.</t>
   </si>
   <si>
-    <t>Transportation Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Serious Incidents Expires (Twyla)</t>
+    <t>Transportation Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Serious Incidents Expires (Rowan)</t>
   </si>
   <si>
     <t>Adaeze Carver-Hargrove</t>
@@ -364,7 +364,7 @@
     <t>Iverson-Ibarra, Rosalind K.</t>
   </si>
   <si>
-    <t>Monthly Documents and Logs Expires (Twyla)</t>
+    <t>Monthly Documents and Logs Expires (Rowan)</t>
   </si>
   <si>
     <t>Valid Vehicle Insurance Expires (2010 Dodge Van)</t>
@@ -379,7 +379,7 @@
     <t>Rasmussen-Ondrejka, Lorcan</t>
   </si>
   <si>
-    <t>Specialized Behaviors Expires (Twyla)</t>
+    <t>Specialized Behaviors Expires (Rowan)</t>
   </si>
   <si>
     <t>Quintero-Hargrove, Ulises</t>
@@ -397,46 +397,46 @@
     <t>Vasquez-Silvestri, Camille</t>
   </si>
   <si>
-    <t>Human Trafficking Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>SIDS Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Medical Consent Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Emergency-Disaster Preparedness Expires (Sharon)</t>
-  </si>
-  <si>
-    <t>EBI Expires (Mae)</t>
-  </si>
-  <si>
-    <t>EBI Expires (Faye)</t>
+    <t>Human Trafficking Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>SIDS Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Medical Consent Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Emergency-Disaster Preparedness Expires (Ilya)</t>
+  </si>
+  <si>
+    <t>EBI Expires (Yarrow)</t>
+  </si>
+  <si>
+    <t>EBI Expires (Anouk)</t>
   </si>
   <si>
     <t>Camille Villanueva-Thibodeaux</t>
   </si>
   <si>
-    <t>Trauma Informed Care (6hrs) Expires (Natasha, Tremel)</t>
-  </si>
-  <si>
-    <t>PRIDE Certificate Expires (Natasha, Tremel)</t>
-  </si>
-  <si>
-    <t>Sexual Abuse Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (6hrs) Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Child Development Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Pet Vaccinations Expires (Zoey)</t>
-  </si>
-  <si>
-    <t>Psychotropic Medication Expires (Twyla)</t>
+    <t>Trauma Informed Care (6hrs) Expires (Cassian, Cassian)</t>
+  </si>
+  <si>
+    <t>PRIDE Certificate Expires (Cassian, Cassian)</t>
+  </si>
+  <si>
+    <t>Sexual Abuse Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Trauma Informed Care (6hrs) Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Child Development Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Pet Vaccinations Expires (Ilya)</t>
+  </si>
+  <si>
+    <t>Psychotropic Medication Expires (Rowan)</t>
   </si>
   <si>
     <t>Thibodeaux-Grantham, Uma</t>
@@ -448,43 +448,43 @@
     <t>Tanaka-Ondrejka, Rafferty</t>
   </si>
   <si>
-    <t>Valid Vehicle Insurance Expires (Volks)</t>
+    <t>Valid Vehicle Insurance Expires (Fintan)</t>
   </si>
   <si>
     <t>Gallagher-Zabala, Oscar L.</t>
   </si>
   <si>
-    <t>Pet Vaccinations Expires (Toby)</t>
-  </si>
-  <si>
-    <t>Pet Vaccinations Expires (Beauty)</t>
-  </si>
-  <si>
-    <t>Separation and Loss Expires (Terica)</t>
-  </si>
-  <si>
-    <t>PAPH Expires (Terica)</t>
-  </si>
-  <si>
-    <t>EBI Expires (Jeffica)</t>
-  </si>
-  <si>
-    <t>Human Trafficking Expires (Terica)</t>
-  </si>
-  <si>
-    <t>EBI Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>PAPH Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Suicide Training Expires (Joseph)</t>
-  </si>
-  <si>
-    <t>PRIDE Certificate Expires (Terica)</t>
-  </si>
-  <si>
-    <t>Picture of Vehicle Inspection Sticker Expires (Volks)</t>
+    <t>Pet Vaccinations Expires (Kestrel)</t>
+  </si>
+  <si>
+    <t>Pet Vaccinations Expires (Halcyon)</t>
+  </si>
+  <si>
+    <t>Separation and Loss Expires (Fenwick)</t>
+  </si>
+  <si>
+    <t>PAPH Expires (Fenwick)</t>
+  </si>
+  <si>
+    <t>EBI Expires (Greer)</t>
+  </si>
+  <si>
+    <t>Human Trafficking Expires (Fenwick)</t>
+  </si>
+  <si>
+    <t>EBI Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>PAPH Expires (Rowan)</t>
+  </si>
+  <si>
+    <t>Suicide Training Expires (Perpetua)</t>
+  </si>
+  <si>
+    <t>PRIDE Certificate Expires (Fenwick)</t>
+  </si>
+  <si>
+    <t>Picture of Vehicle Inspection Sticker Expires (Fintan)</t>
   </si>
   <si>
     <t>Waverly-Jarrett, Wren</t>
@@ -502,46 +502,43 @@
     <t>Underhill-Oyelaran, Xavier</t>
   </si>
   <si>
-    <t>Houston Strong Town Hall Meeting #1 Expires (Natasha, Tremel)</t>
-  </si>
-  <si>
-    <t>Houston Strong Town Hall Meeting #1 Expires (Chantelle, Mikeisha)</t>
-  </si>
-  <si>
-    <t>Serious Incidents Expires (Chantelle, Mikeisha)</t>
-  </si>
-  <si>
-    <t>SIDS Expires (Chantelle, Mikeisha)</t>
-  </si>
-  <si>
-    <t>Health and Safety Expires (Chantelle, Mikeisha)</t>
-  </si>
-  <si>
-    <t>PAPH Expires (Bridjett, Ardis)</t>
-  </si>
-  <si>
-    <t>Human Trafficking Expires (Bridjett, Ardis)</t>
-  </si>
-  <si>
-    <t>Suicide Training Expires (Sherry)</t>
-  </si>
-  <si>
-    <t>Levels of Care Expires (Sherry)</t>
-  </si>
-  <si>
-    <t>Level of Care Expires (Twyla)</t>
-  </si>
-  <si>
-    <t>Human Trafficking Expires (Israel)</t>
+    <t>Houston Strong Town Hall Meeting #1 Expires (Cassian, Cassian)</t>
+  </si>
+  <si>
+    <t>Houston Strong Town Hall Meeting #1 Expires (Ursula, Jethro)</t>
+  </si>
+  <si>
+    <t>Serious Incidents Expires (Ursula, Jethro)</t>
+  </si>
+  <si>
+    <t>SIDS Expires (Ursula, Jethro)</t>
+  </si>
+  <si>
+    <t>Health and Safety Expires (Ursula, Jethro)</t>
+  </si>
+  <si>
+    <t>PAPH Expires (Fintan, Ursula)</t>
+  </si>
+  <si>
+    <t>Human Trafficking Expires (Fintan, Ursula)</t>
+  </si>
+  <si>
+    <t>Suicide Training Expires (Eulalia)</t>
+  </si>
+  <si>
+    <t>Levels of Care Expires (Eulalia)</t>
+  </si>
+  <si>
+    <t>Level of Care Expires (Rowan)</t>
   </si>
   <si>
     <t>Kensington-Lindqvist, Gemma</t>
   </si>
   <si>
-    <t>Trauma Informed Care (2hrs) Expires (Chantelle, Mikeisha)</t>
-  </si>
-  <si>
-    <t>Reporting Child Abuse and Neglect Expires (Natasha, Tremel)</t>
+    <t>Trauma Informed Care (2hrs) Expires (Ursula, Jethro)</t>
+  </si>
+  <si>
+    <t>Reporting Child Abuse and Neglect Expires (Cassian, Cassian)</t>
   </si>
   <si>
     <t>Drivers Record (Parent A) Expires</t>
@@ -562,16 +559,16 @@
     <t>Carver-Prescott, Quincy</t>
   </si>
   <si>
-    <t>Sexual Abuse Expires (Jaquavia, Lashena)</t>
-  </si>
-  <si>
-    <t>Houston Strong Town Hall Meeting #2 Expires (Israel)</t>
+    <t>Sexual Abuse Expires (Rowan, Kestrel)</t>
+  </si>
+  <si>
+    <t>Houston Strong Town Hall Meeting #2 Expires (Rowan)</t>
   </si>
   <si>
     <t>Rasmussen-Dunmore, Camille</t>
   </si>
   <si>
-    <t>Human Trafficking Expires (Sherry)</t>
+    <t>Human Trafficking Expires (Eulalia)</t>
   </si>
   <si>
     <t>Jarrett-Kowalski, Tamsin</t>
@@ -580,7 +577,7 @@
     <t>Northcott-Quimby, Lorcan</t>
   </si>
   <si>
-    <t>Cultural Competency Expires (Sharon)</t>
+    <t>Cultural Competency Expires (Ilya)</t>
   </si>
   <si>
     <t>Kensington-Jennings, Thaddeus</t>
@@ -589,7 +586,7 @@
     <t>Vasquez-Castellanos, Thaddeus</t>
   </si>
   <si>
-    <t>Valid Vehicle Insurance Expires (Israel Adebayo Olugbeje)</t>
+    <t>Valid Vehicle Insurance Expires (Briony)</t>
   </si>
   <si>
     <t>Ashford-Xiong, Wren</t>
@@ -601,97 +598,88 @@
     <t>Anticipated Off Hold</t>
   </si>
   <si>
-    <t>Minimum Standards Expires (Terica)</t>
-  </si>
-  <si>
-    <t>Minimum Standards Expires (Chantelle, Mikeisha)</t>
-  </si>
-  <si>
-    <t>Minimum Standards Expires (Sharon)</t>
-  </si>
-  <si>
-    <t>Minimum Standards Expires (Israel)</t>
+    <t>Minimum Standards Expires (Fenwick)</t>
+  </si>
+  <si>
+    <t>Minimum Standards Expires (Ursula, Jethro)</t>
+  </si>
+  <si>
+    <t>Minimum Standards Expires (Ilya)</t>
   </si>
   <si>
     <t>Mbeki-Ashford, Keziah A.</t>
   </si>
   <si>
-    <t>Bloodborne Pathogens Expires (Shalaundra)</t>
-  </si>
-  <si>
-    <t>Suicide Training Expires (Shalaundra)</t>
-  </si>
-  <si>
-    <t>Medication Management Expires (Shalaundra)</t>
-  </si>
-  <si>
-    <t>Bloodborne Pathogens Expires (Israel)</t>
-  </si>
-  <si>
-    <t>Houston Strong Town Hall Meeting #2 Expires (Natasha, Tremel)</t>
-  </si>
-  <si>
-    <t>Houston Strong Town Hall Meeting #2 Expires (Chantelle, Mikeisha)</t>
-  </si>
-  <si>
-    <t>Emergency-Disaster Preparedness Expires (Chantelle, Mikeisha)</t>
-  </si>
-  <si>
-    <t>Emergency-Disaster Preparedness Expires (Bridjett, Ardis)</t>
-  </si>
-  <si>
-    <t>Bloodborne Pathogens Expires (Bridjett, Ardis)</t>
-  </si>
-  <si>
-    <t>Houston Strong Town Hall Meeting #1 Expires (Bridjett)</t>
-  </si>
-  <si>
-    <t>Levels of Care Expires (Israel)</t>
+    <t>Bloodborne Pathogens Expires (Anouk)</t>
+  </si>
+  <si>
+    <t>Suicide Training Expires (Anouk)</t>
+  </si>
+  <si>
+    <t>Medication Management Expires (Anouk)</t>
+  </si>
+  <si>
+    <t>Houston Strong Town Hall Meeting #2 Expires (Cassian, Cassian)</t>
+  </si>
+  <si>
+    <t>Houston Strong Town Hall Meeting #2 Expires (Ursula, Jethro)</t>
+  </si>
+  <si>
+    <t>Emergency-Disaster Preparedness Expires (Ursula, Jethro)</t>
+  </si>
+  <si>
+    <t>Emergency-Disaster Preparedness Expires (Fintan, Ursula)</t>
+  </si>
+  <si>
+    <t>Bloodborne Pathogens Expires (Fintan, Ursula)</t>
+  </si>
+  <si>
+    <t>Houston Strong Town Hall Meeting #1 Expires (Fintan)</t>
+  </si>
+  <si>
+    <t>Levels of Care Expires (Rowan)</t>
   </si>
   <si>
     <t>Nakamura-Rasmussen, Quincy S.</t>
   </si>
   <si>
-    <t>Normalcy Expires (Titus)</t>
-  </si>
-  <si>
-    <t>Psychotropic Medication Expires (Titus)</t>
-  </si>
-  <si>
-    <t>Medical Consent Expires (Titus)</t>
-  </si>
-  <si>
-    <t>Medical Consent Expires (Happiness)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (6hrs) Expires (Happiness)</t>
-  </si>
-  <si>
-    <t>Psychotropic Medication Expires (Happiness)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (2hrs) Expires (Happiness)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (2hrs) Expires (Titus)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (6hrs) Expires (Titus)</t>
-  </si>
-  <si>
-    <t>Normalcy Expires (Happiness)</t>
-  </si>
-  <si>
-    <t>Sexual Abuse Expires (Titus)</t>
-  </si>
-  <si>
-    <t>Sexual Abuse Expires (Happiness)</t>
-  </si>
-  <si>
-    <t>Picture of Vehicle Inspection Sticker Expires (Dodge Charger)</t>
-  </si>
-  <si>
-    <t>Picture of Vehicle Inspection Sticker Expires (Toyota Land Cruiser)</t>
+    <t>Normalcy Expires (Halcyon)</t>
+  </si>
+  <si>
+    <t>Psychotropic Medication Expires (Halcyon)</t>
+  </si>
+  <si>
+    <t>Medical Consent Expires (Halcyon)</t>
+  </si>
+  <si>
+    <t>Medical Consent Expires (Ines)</t>
+  </si>
+  <si>
+    <t>Trauma Informed Care (6hrs) Expires (Ines)</t>
+  </si>
+  <si>
+    <t>Psychotropic Medication Expires (Ines)</t>
+  </si>
+  <si>
+    <t>Trauma Informed Care (2hrs) Expires (Ines)</t>
+  </si>
+  <si>
+    <t>Trauma Informed Care (2hrs) Expires (Halcyon)</t>
+  </si>
+  <si>
+    <t>Trauma Informed Care (6hrs) Expires (Halcyon)</t>
+  </si>
+  <si>
+    <t>Normalcy Expires (Ines)</t>
+  </si>
+  <si>
+    <t>Sexual Abuse Expires (Ines)</t>
+  </si>
+  <si>
+    <t>Picture of Vehicle Inspection Sticker Expires (Ilya)</t>
+  </si>
+  <si>
+    <t>Picture of Vehicle Inspection Sticker Expires (Cleo)</t>
   </si>
   <si>
     <t>Picture of Vehicle Inspection Sticker Expires (Toyota Rav4 (2020))</t>
@@ -700,16 +688,13 @@
     <t>Picture of Vehicle Inspection Sticker Expires (Toyota Rav4)</t>
   </si>
   <si>
-    <t>Picture of Vehicle Inspection Sticker Expires (Audi)</t>
-  </si>
-  <si>
-    <t>Emergency-Disaster Preparedness Expires (Joseph)</t>
+    <t>Emergency-Disaster Preparedness Expires (Perpetua)</t>
   </si>
   <si>
     <t>Northcott-Dunmore, Ulises G.</t>
   </si>
   <si>
-    <t>Sexual Abuse Expires (Joseph)</t>
+    <t>Sexual Abuse Expires (Perpetua)</t>
   </si>
   <si>
     <t>Nadia Farrow-Eastwood</t>
@@ -721,16 +706,16 @@
     <t>Ashford-Larkin, Verity</t>
   </si>
   <si>
-    <t>Emergency-Disaster Preparedness Expires (Titus, Happiness)</t>
-  </si>
-  <si>
-    <t>Picture of Vehicle Inspection Sticker Expires (Mercedes)</t>
-  </si>
-  <si>
-    <t>Reporting Child Abuse and Neglect Expires (Sherry)</t>
-  </si>
-  <si>
-    <t>Sexual Abuse Expires (Sharon)</t>
+    <t>Emergency-Disaster Preparedness Expires (Halcyon, Ines)</t>
+  </si>
+  <si>
+    <t>Picture of Vehicle Inspection Sticker Expires (Zinnia)</t>
+  </si>
+  <si>
+    <t>Reporting Child Abuse and Neglect Expires (Eulalia)</t>
+  </si>
+  <si>
+    <t>Sexual Abuse Expires (Ilya)</t>
   </si>
   <si>
     <t>Yoshida-Nakamura, Xavier</t>
@@ -742,22 +727,19 @@
     <t>Fontaine-Nakamura, Rosalind P.</t>
   </si>
   <si>
-    <t>Picture of Vehicle Inspection Sticker Expires (Israel Adebayo Olugbeje)</t>
-  </si>
-  <si>
-    <t>Picture of Vehicle Inspection Sticker Expires (Dodge)</t>
-  </si>
-  <si>
-    <t>Picture of Vehicle Inspection Sticker Expires (Jeep)</t>
-  </si>
-  <si>
-    <t>Monthly Documents and Logs Expires (Titus)</t>
+    <t>Picture of Vehicle Inspection Sticker Expires (Briony)</t>
+  </si>
+  <si>
+    <t>Picture of Vehicle Inspection Sticker Expires (Linnea)</t>
+  </si>
+  <si>
+    <t>Monthly Documents and Logs Expires (Halcyon)</t>
   </si>
   <si>
     <t>Hollis-Sandoval, Leonie</t>
   </si>
   <si>
-    <t>Valid Vehicle Insurance Expires (Dodge Charger)</t>
+    <t>Valid Vehicle Insurance Expires (Ilya)</t>
   </si>
   <si>
     <t>Ueda-Yardley, Yusuf</t>
@@ -769,46 +751,43 @@
     <t>Carver-Eastwood, Bodhi</t>
   </si>
   <si>
-    <t>Child Development Expires (Jeffica)</t>
-  </si>
-  <si>
-    <t>Child Development Expires (Chantelle, Mikeisha)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (6hrs) Expires (Lakiesha, Yigni)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (6hrs) Expires (Jaquavia, Lashena)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (6hrs) Expires (Sherry)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (6hrs) Expires (Israel)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (6hrs) Expires (Bridjett, Ardis)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (6hrs) Expires (Faye)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (6hrs) Expires (Chantelle, Mikeisha)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (6hrs) Expires (Terica)</t>
-  </si>
-  <si>
-    <t>Trauma Informed Care (6hrs) Expires (Jeffica)</t>
+    <t>Child Development Expires (Greer)</t>
+  </si>
+  <si>
+    <t>Child Development Expires (Ursula, Jethro)</t>
+  </si>
+  <si>
+    <t>Trauma Informed Care (6hrs) Expires (Cleo, Alder)</t>
+  </si>
+  <si>
+    <t>Trauma Informed Care (6hrs) Expires (Rowan, Kestrel)</t>
+  </si>
+  <si>
+    <t>Trauma Informed Care (6hrs) Expires (Eulalia)</t>
+  </si>
+  <si>
+    <t>Trauma Informed Care (6hrs) Expires (Fintan, Ursula)</t>
+  </si>
+  <si>
+    <t>Trauma Informed Care (6hrs) Expires (Anouk)</t>
+  </si>
+  <si>
+    <t>Trauma Informed Care (6hrs) Expires (Ursula, Jethro)</t>
+  </si>
+  <si>
+    <t>Trauma Informed Care (6hrs) Expires (Fenwick)</t>
+  </si>
+  <si>
+    <t>Trauma Informed Care (6hrs) Expires (Greer)</t>
   </si>
   <si>
     <t>Valid Vehicle Insurance Expires (2018 Chevrolet)</t>
   </si>
   <si>
-    <t>PRIDE Certificate Expires (Michelle)</t>
-  </si>
-  <si>
-    <t>Valid Vehicle Insurance Expires (Cadillac)</t>
+    <t>PRIDE Certificate Expires (Perpetua)</t>
+  </si>
+  <si>
+    <t>Valid Vehicle Insurance Expires (Cleo)</t>
   </si>
   <si>
     <t>Dunmore-Northcott, Esperanza</t>
@@ -817,7 +796,7 @@
     <t>Valid Vehicle Insurance Expires (Mercedes-Benz)</t>
   </si>
   <si>
-    <t>Sexual Abuse Expires (Faye)</t>
+    <t>Sexual Abuse Expires (Anouk)</t>
   </si>
   <si>
     <t>Discharge Closure Summary</t>
@@ -826,37 +805,34 @@
     <t>Lindqvist-Gallagher, Niamh</t>
   </si>
   <si>
-    <t>Cultural Competency Expires (Chantelle, Mikeisha)</t>
-  </si>
-  <si>
-    <t>Separation and Loss Expires (Joseph)</t>
-  </si>
-  <si>
-    <t>SIDS Expires (Shalaundra)</t>
-  </si>
-  <si>
-    <t>Monthly Documents and Logs Expires (Bridjett, Ardis)</t>
-  </si>
-  <si>
-    <t>Separation and Loss Expires (Bridjett, Ardis)</t>
-  </si>
-  <si>
-    <t>SIDS Expires (Cristina)</t>
-  </si>
-  <si>
-    <t>Separation and Loss Expires (Jeffica)</t>
-  </si>
-  <si>
-    <t>Separation and Loss Expires (Titus, Happiness)</t>
-  </si>
-  <si>
-    <t>Medication Management Expires (Titus, Happiness)</t>
-  </si>
-  <si>
-    <t>Separation and Loss Expires (Israel)</t>
-  </si>
-  <si>
-    <t>Houston Strong Town Hall Meeting #2 Expires (Bridjett)</t>
+    <t>Cultural Competency Expires (Ursula, Jethro)</t>
+  </si>
+  <si>
+    <t>Separation and Loss Expires (Perpetua)</t>
+  </si>
+  <si>
+    <t>SIDS Expires (Anouk)</t>
+  </si>
+  <si>
+    <t>Monthly Documents and Logs Expires (Fintan, Ursula)</t>
+  </si>
+  <si>
+    <t>Separation and Loss Expires (Fintan, Ursula)</t>
+  </si>
+  <si>
+    <t>SIDS Expires (Vesper)</t>
+  </si>
+  <si>
+    <t>Separation and Loss Expires (Greer)</t>
+  </si>
+  <si>
+    <t>Separation and Loss Expires (Halcyon, Ines)</t>
+  </si>
+  <si>
+    <t>Medication Management Expires (Halcyon, Ines)</t>
+  </si>
+  <si>
+    <t>Houston Strong Town Hall Meeting #2 Expires (Fintan)</t>
   </si>
   <si>
     <t>Hollis-Yardley, Felix L.</t>
@@ -865,52 +841,43 @@
     <t>Valid Vehicle Insurance Expires (2020)</t>
   </si>
   <si>
-    <t>Medical Consent Expires (Mikeisha)</t>
-  </si>
-  <si>
-    <t>Normalcy Expires (Mikeisha)</t>
-  </si>
-  <si>
-    <t>Reporting Child Abuse and Neglect Expires (Sharon)</t>
-  </si>
-  <si>
-    <t>Medical Consent Expires (Chantelle)</t>
-  </si>
-  <si>
-    <t>Normalcy Expires (Chantelle)</t>
-  </si>
-  <si>
-    <t>Pet Vaccinations Expires (Orion)</t>
-  </si>
-  <si>
-    <t>EBI Expires (Michelle)</t>
-  </si>
-  <si>
-    <t>EBI Expires (Joseph)</t>
-  </si>
-  <si>
-    <t>EBI Expires (Sherry)</t>
-  </si>
-  <si>
-    <t>EBI Expires (Shalaundra)</t>
-  </si>
-  <si>
-    <t>EBI Expires (Titus, Happiness)</t>
-  </si>
-  <si>
-    <t>EBI Expires (Natasha, Tremel)</t>
-  </si>
-  <si>
-    <t>EBI Expires (Bridjett, Ardis)</t>
-  </si>
-  <si>
-    <t>EBI Expires (Cristina)</t>
-  </si>
-  <si>
-    <t>EBI Expires (Israel)</t>
-  </si>
-  <si>
-    <t>Valid Drivers License Expires (Frank Arthur)</t>
+    <t>Medical Consent Expires (Jethro)</t>
+  </si>
+  <si>
+    <t>Normalcy Expires (Jethro)</t>
+  </si>
+  <si>
+    <t>Reporting Child Abuse and Neglect Expires (Ilya)</t>
+  </si>
+  <si>
+    <t>Medical Consent Expires (Ursula)</t>
+  </si>
+  <si>
+    <t>Normalcy Expires (Ursula)</t>
+  </si>
+  <si>
+    <t>Pet Vaccinations Expires (Ximena)</t>
+  </si>
+  <si>
+    <t>EBI Expires (Perpetua)</t>
+  </si>
+  <si>
+    <t>EBI Expires (Eulalia)</t>
+  </si>
+  <si>
+    <t>EBI Expires (Halcyon, Ines)</t>
+  </si>
+  <si>
+    <t>EBI Expires (Cassian, Cassian)</t>
+  </si>
+  <si>
+    <t>EBI Expires (Fintan, Ursula)</t>
+  </si>
+  <si>
+    <t>EBI Expires (Vesper)</t>
+  </si>
+  <si>
+    <t>Valid Drivers License Expires (Cassian)</t>
   </si>
 </sst>
 </file>
@@ -5745,7 +5712,7 @@
         <v>9</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>26</v>
@@ -5777,7 +5744,7 @@
         <v>71</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>28</v>
@@ -5803,7 +5770,7 @@
         <v>71</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>28</v>
@@ -5823,7 +5790,7 @@
         <v>9</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>34</v>
@@ -5849,7 +5816,7 @@
         <v>9</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>34</v>
@@ -5875,7 +5842,7 @@
         <v>9</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>58</v>
@@ -5959,7 +5926,7 @@
         <v>26</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>28</v>
@@ -6037,10 +6004,10 @@
         <v>71</v>
       </c>
       <c r="F182" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G182" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="G182" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>0</v>
@@ -6089,7 +6056,7 @@
         <v>26</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>28</v>
@@ -6115,7 +6082,7 @@
         <v>26</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>28</v>
@@ -6141,7 +6108,7 @@
         <v>26</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>28</v>
@@ -6187,7 +6154,7 @@
         <v>9</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>58</v>
@@ -6265,7 +6232,7 @@
         <v>9</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>26</v>
@@ -6297,10 +6264,10 @@
         <v>34</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>0</v>
@@ -6317,7 +6284,7 @@
         <v>9</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>58</v>
@@ -6349,7 +6316,7 @@
         <v>161</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>13</v>
@@ -6401,7 +6368,7 @@
         <v>58</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>28</v>
@@ -6427,7 +6394,7 @@
         <v>71</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>28</v>
@@ -6447,7 +6414,7 @@
         <v>9</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>26</v>
@@ -6479,10 +6446,10 @@
         <v>71</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>0</v>
@@ -6505,7 +6472,7 @@
         <v>34</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>28</v>
@@ -6551,7 +6518,7 @@
         <v>9</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>26</v>
@@ -6583,7 +6550,7 @@
         <v>11</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>13</v>
@@ -6600,19 +6567,19 @@
         <v>46112</v>
       </c>
       <c r="C204" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D204" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="D204" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>34</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>0</v>
@@ -6635,7 +6602,7 @@
         <v>26</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>28</v>
@@ -6661,7 +6628,7 @@
         <v>26</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>28</v>
@@ -6681,7 +6648,7 @@
         <v>9</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>71</v>
@@ -6707,7 +6674,7 @@
         <v>9</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>34</v>
@@ -6733,7 +6700,7 @@
         <v>9</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>26</v>
@@ -6811,7 +6778,7 @@
         <v>9</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>26</v>
@@ -6843,7 +6810,7 @@
         <v>134</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>28</v>
@@ -6869,7 +6836,7 @@
         <v>134</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>28</v>
@@ -6889,7 +6856,7 @@
         <v>9</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>43</v>
@@ -6915,7 +6882,7 @@
         <v>9</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>43</v>
@@ -6941,7 +6908,7 @@
         <v>9</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>43</v>
@@ -6967,7 +6934,7 @@
         <v>9</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>204</v>
+        <v>83</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>26</v>
@@ -6993,7 +6960,7 @@
         <v>9</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>34</v>
@@ -7019,7 +6986,7 @@
         <v>9</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>34</v>
@@ -7045,7 +7012,7 @@
         <v>9</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>34</v>
@@ -7071,7 +7038,7 @@
         <v>9</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>58</v>
@@ -7097,7 +7064,7 @@
         <v>9</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>58</v>
@@ -7123,7 +7090,7 @@
         <v>9</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>58</v>
@@ -7149,7 +7116,7 @@
         <v>9</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>26</v>
@@ -7181,7 +7148,7 @@
         <v>20</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>13</v>
@@ -7233,7 +7200,7 @@
         <v>26</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>28</v>
@@ -7253,7 +7220,7 @@
         <v>9</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>134</v>
@@ -7279,7 +7246,7 @@
         <v>9</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>134</v>
@@ -7305,7 +7272,7 @@
         <v>9</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>134</v>
@@ -7331,7 +7298,7 @@
         <v>9</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>134</v>
@@ -7357,7 +7324,7 @@
         <v>9</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>134</v>
@@ -7383,7 +7350,7 @@
         <v>9</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>134</v>
@@ -7409,7 +7376,7 @@
         <v>9</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>134</v>
@@ -7435,7 +7402,7 @@
         <v>9</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>134</v>
@@ -7461,7 +7428,7 @@
         <v>9</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>134</v>
@@ -7487,7 +7454,7 @@
         <v>9</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>134</v>
@@ -7513,7 +7480,7 @@
         <v>9</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>223</v>
+        <v>101</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>134</v>
@@ -7539,7 +7506,7 @@
         <v>9</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>134</v>
@@ -7565,7 +7532,7 @@
         <v>9</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>134</v>
@@ -7591,7 +7558,7 @@
         <v>9</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>134</v>
@@ -7617,7 +7584,7 @@
         <v>9</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>134</v>
@@ -7643,7 +7610,7 @@
         <v>9</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>134</v>
@@ -7675,7 +7642,7 @@
         <v>11</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>13</v>
@@ -7701,7 +7668,7 @@
         <v>11</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>13</v>
@@ -7721,7 +7688,7 @@
         <v>9</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>11</v>
@@ -7747,7 +7714,7 @@
         <v>9</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>58</v>
@@ -7805,7 +7772,7 @@
         <v>161</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>13</v>
@@ -7825,7 +7792,7 @@
         <v>9</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>58</v>
@@ -7880,13 +7847,13 @@
         <v>49</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>0</v>
@@ -7909,7 +7876,7 @@
         <v>20</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>13</v>
@@ -7935,7 +7902,7 @@
         <v>20</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>13</v>
@@ -7961,7 +7928,7 @@
         <v>20</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>13</v>
@@ -7981,7 +7948,7 @@
         <v>9</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>134</v>
@@ -8013,10 +7980,10 @@
         <v>71</v>
       </c>
       <c r="F258" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G258" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="G258" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>0</v>
@@ -8065,7 +8032,7 @@
         <v>58</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>28</v>
@@ -8143,7 +8110,7 @@
         <v>26</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>28</v>
@@ -8163,7 +8130,7 @@
         <v>9</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>26</v>
@@ -8195,7 +8162,7 @@
         <v>26</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>28</v>
@@ -8299,10 +8266,10 @@
         <v>34</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>0</v>
@@ -8371,7 +8338,7 @@
         <v>9</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>58</v>
@@ -8403,10 +8370,10 @@
         <v>71</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>0</v>
@@ -8423,7 +8390,7 @@
         <v>9</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>26</v>
@@ -8481,7 +8448,7 @@
         <v>20</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>13</v>
@@ -8507,7 +8474,7 @@
         <v>26</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>28</v>
@@ -8533,7 +8500,7 @@
         <v>20</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>13</v>
@@ -8559,7 +8526,7 @@
         <v>11</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>13</v>
@@ -8605,7 +8572,7 @@
         <v>9</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>26</v>
@@ -8631,7 +8598,7 @@
         <v>9</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>26</v>
@@ -8657,13 +8624,13 @@
         <v>9</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>71</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>28</v>
@@ -8689,7 +8656,7 @@
         <v>26</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>28</v>
@@ -8706,10 +8673,10 @@
         <v>46204</v>
       </c>
       <c r="C285" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D285" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>52</v>
@@ -8767,7 +8734,7 @@
         <v>161</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>13</v>
@@ -8787,7 +8754,7 @@
         <v>9</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>134</v>
@@ -8819,7 +8786,7 @@
         <v>11</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>13</v>
@@ -8891,7 +8858,7 @@
         <v>9</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>134</v>
@@ -8923,7 +8890,7 @@
         <v>11</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>13</v>
@@ -8949,7 +8916,7 @@
         <v>11</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>13</v>
@@ -9001,7 +8968,7 @@
         <v>134</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>28</v>
@@ -9053,7 +9020,7 @@
         <v>20</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>13</v>
@@ -9079,7 +9046,7 @@
         <v>11</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>13</v>
@@ -9177,7 +9144,7 @@
         <v>9</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>26</v>
@@ -9203,7 +9170,7 @@
         <v>9</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>34</v>
@@ -9229,7 +9196,7 @@
         <v>9</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>34</v>
@@ -9255,7 +9222,7 @@
         <v>9</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>58</v>
@@ -9281,7 +9248,7 @@
         <v>9</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>58</v>
@@ -9307,7 +9274,7 @@
         <v>9</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>257</v>
+        <v>138</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>26</v>
@@ -9333,7 +9300,7 @@
         <v>9</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>58</v>
@@ -9359,7 +9326,7 @@
         <v>9</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>134</v>
@@ -9385,7 +9352,7 @@
         <v>9</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E311" s="2" t="s">
         <v>34</v>
@@ -9411,7 +9378,7 @@
         <v>9</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>71</v>
@@ -9437,7 +9404,7 @@
         <v>9</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="E313" s="2" t="s">
         <v>26</v>
@@ -9489,7 +9456,7 @@
         <v>9</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>26</v>
@@ -9547,7 +9514,7 @@
         <v>26</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>28</v>
@@ -9573,7 +9540,7 @@
         <v>20</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>13</v>
@@ -9593,7 +9560,7 @@
         <v>9</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>58</v>
@@ -9619,13 +9586,13 @@
         <v>9</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>13</v>
@@ -9677,7 +9644,7 @@
         <v>11</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>13</v>
@@ -9703,7 +9670,7 @@
         <v>115</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>28</v>
@@ -9723,13 +9690,13 @@
         <v>9</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>13</v>
@@ -9827,7 +9794,7 @@
         <v>9</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>134</v>
@@ -9905,13 +9872,13 @@
         <v>14</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>115</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>28</v>
@@ -10041,10 +10008,10 @@
         <v>71</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H336" s="2" t="s">
         <v>0</v>
@@ -10067,7 +10034,7 @@
         <v>11</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>13</v>
@@ -10090,13 +10057,13 @@
         <v>19</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H338" s="2" t="s">
         <v>0</v>
@@ -10113,7 +10080,7 @@
         <v>9</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>34</v>
@@ -10139,7 +10106,7 @@
         <v>9</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>58</v>
@@ -10165,7 +10132,7 @@
         <v>9</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>43</v>
@@ -10191,7 +10158,7 @@
         <v>9</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>58</v>
@@ -10217,7 +10184,7 @@
         <v>9</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>58</v>
@@ -10243,7 +10210,7 @@
         <v>9</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E344" s="2" t="s">
         <v>26</v>
@@ -10269,7 +10236,7 @@
         <v>9</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="E345" s="2" t="s">
         <v>26</v>
@@ -10295,7 +10262,7 @@
         <v>9</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>134</v>
@@ -10321,7 +10288,7 @@
         <v>9</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>134</v>
@@ -10347,7 +10314,7 @@
         <v>9</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>280</v>
+        <v>74</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>26</v>
@@ -10373,7 +10340,7 @@
         <v>9</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>58</v>
@@ -10405,7 +10372,7 @@
         <v>11</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>13</v>
@@ -10431,7 +10398,7 @@
         <v>11</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>13</v>
@@ -10451,7 +10418,7 @@
         <v>14</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>11</v>
@@ -10483,7 +10450,7 @@
         <v>20</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>13</v>
@@ -10509,7 +10476,7 @@
         <v>11</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>13</v>
@@ -10535,7 +10502,7 @@
         <v>20</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>13</v>
@@ -10555,7 +10522,7 @@
         <v>9</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>34</v>
@@ -10581,7 +10548,7 @@
         <v>9</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="E357" s="2" t="s">
         <v>34</v>
@@ -10607,7 +10574,7 @@
         <v>9</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>34</v>
@@ -10633,7 +10600,7 @@
         <v>9</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E359" s="2" t="s">
         <v>26</v>
@@ -10659,7 +10626,7 @@
         <v>9</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="E360" s="2" t="s">
         <v>34</v>
@@ -10685,7 +10652,7 @@
         <v>9</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E361" s="2" t="s">
         <v>34</v>
@@ -10711,13 +10678,13 @@
         <v>9</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E362" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>28</v>
@@ -10763,7 +10730,7 @@
         <v>9</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E364" s="2" t="s">
         <v>58</v>
@@ -10789,7 +10756,7 @@
         <v>9</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="E365" s="2" t="s">
         <v>58</v>
@@ -10815,7 +10782,7 @@
         <v>9</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E366" s="2" t="s">
         <v>58</v>
@@ -10841,7 +10808,7 @@
         <v>9</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>293</v>
+        <v>133</v>
       </c>
       <c r="E367" s="2" t="s">
         <v>43</v>
@@ -10867,7 +10834,7 @@
         <v>9</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="E368" s="2" t="s">
         <v>134</v>
@@ -10893,7 +10860,7 @@
         <v>9</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E369" s="2" t="s">
         <v>34</v>
@@ -10919,7 +10886,7 @@
         <v>9</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="E370" s="2" t="s">
         <v>58</v>
@@ -10945,7 +10912,7 @@
         <v>9</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="E371" s="2" t="s">
         <v>26</v>
@@ -10971,7 +10938,7 @@
         <v>9</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>298</v>
+        <v>153</v>
       </c>
       <c r="E372" s="2" t="s">
         <v>26</v>
@@ -10997,7 +10964,7 @@
         <v>9</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="E373" s="2" t="s">
         <v>11</v>
